--- a/artfynd/A 45781-2019 artfynd.xlsx
+++ b/artfynd/A 45781-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747683</v>
       </c>
       <c r="B2" t="n">
-        <v>78396</v>
+        <v>78498</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45781-2019 artfynd.xlsx
+++ b/artfynd/A 45781-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747683</v>
       </c>
       <c r="B2" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45781-2019 artfynd.xlsx
+++ b/artfynd/A 45781-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747683</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45781-2019 artfynd.xlsx
+++ b/artfynd/A 45781-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747683</v>
       </c>
       <c r="B2" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Sanna Strömberg</t>
+          <t>Sanna Strömberg , Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
